--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C. D. MENSAJERO ISLA DE LA PALMA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C. D. MENSAJERO ISLA DE LA PALMA.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>94.6922</v>
+        <v>116.579</v>
       </c>
       <c r="E2" t="n">
-        <v>90.9676</v>
+        <v>107.2308</v>
       </c>
       <c r="F2" t="n">
-        <v>3.725</v>
+        <v>9.349</v>
       </c>
       <c r="G2" t="n">
         <v>65.8995</v>
@@ -610,13 +610,13 @@
         <v>61.7022</v>
       </c>
       <c r="S2" t="n">
-        <v>-30.2976</v>
+        <v>-8.41</v>
       </c>
       <c r="T2" t="n">
-        <v>-22.5121</v>
+        <v>-6.2488</v>
       </c>
       <c r="U2" t="n">
-        <v>-7.7855</v>
+        <v>-2.1614</v>
       </c>
       <c r="V2" t="n">
         <v>63.9407</v>
@@ -643,13 +643,13 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>42.4436</v>
+        <v>32.6416</v>
       </c>
       <c r="E3" t="n">
-        <v>38.6892</v>
+        <v>32.8515</v>
       </c>
       <c r="F3" t="n">
-        <v>3.754400000000001</v>
+        <v>-0.2101000000000007</v>
       </c>
       <c r="G3" t="n">
         <v>3.482800000000001</v>
@@ -688,13 +688,13 @@
         <v>52.5829</v>
       </c>
       <c r="S3" t="n">
-        <v>16.6212</v>
+        <v>6.8191</v>
       </c>
       <c r="T3" t="n">
-        <v>9.5245</v>
+        <v>3.6868</v>
       </c>
       <c r="U3" t="n">
-        <v>7.0963</v>
+        <v>3.1323</v>
       </c>
       <c r="V3" t="n">
         <v>0.9963999999999995</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. NIANG</t>
+          <t>P. RODRIGUEZ RIVERO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>28.3865</v>
+        <v>13.3549</v>
       </c>
       <c r="E4" t="n">
-        <v>20.4551</v>
+        <v>10.3836</v>
       </c>
       <c r="F4" t="n">
-        <v>7.9311</v>
+        <v>2.9714</v>
       </c>
       <c r="G4" t="n">
-        <v>11.9646</v>
+        <v>-7.000600000000002</v>
       </c>
       <c r="H4" t="n">
-        <v>18.572</v>
+        <v>-4.876200000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-6.6076</v>
+        <v>-2.1243</v>
       </c>
       <c r="J4" t="n">
-        <v>35.7047</v>
+        <v>28.0764</v>
       </c>
       <c r="K4" t="n">
-        <v>31.4724</v>
+        <v>13.5162</v>
       </c>
       <c r="L4" t="n">
-        <v>4.2325</v>
+        <v>14.5604</v>
       </c>
       <c r="M4" t="n">
-        <v>-23.7401</v>
+        <v>-35.0774</v>
       </c>
       <c r="N4" t="n">
-        <v>-12.9007</v>
+        <v>-18.3927</v>
       </c>
       <c r="O4" t="n">
-        <v>-10.8395</v>
+        <v>-16.6845</v>
       </c>
       <c r="P4" t="n">
-        <v>-20.7613</v>
+        <v>-8.5373</v>
       </c>
       <c r="Q4" t="n">
-        <v>-55.8812</v>
+        <v>-67.32939999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>35.12</v>
+        <v>58.7918</v>
       </c>
       <c r="S4" t="n">
-        <v>27.4203</v>
+        <v>2.2823</v>
       </c>
       <c r="T4" t="n">
-        <v>17.7696</v>
+        <v>2.669700000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>9.651299999999999</v>
+        <v>-0.3871000000000002</v>
       </c>
       <c r="V4" t="n">
-        <v>9.7628</v>
+        <v>26.6107</v>
       </c>
       <c r="W4" t="n">
-        <v>22.8624</v>
+        <v>46.9668</v>
       </c>
       <c r="X4" t="n">
-        <v>-13.0997</v>
+        <v>-20.356</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ RIVERO</t>
+          <t>M. NIANG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
-        <v>14.4721</v>
+        <v>12.2274</v>
       </c>
       <c r="E5" t="n">
-        <v>12.5572</v>
+        <v>9.330699999999998</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9149</v>
+        <v>2.896800000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>-7.000600000000002</v>
+        <v>11.9646</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.876200000000001</v>
+        <v>18.572</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.1243</v>
+        <v>-6.6076</v>
       </c>
       <c r="J5" t="n">
-        <v>28.0764</v>
+        <v>35.7047</v>
       </c>
       <c r="K5" t="n">
-        <v>13.5162</v>
+        <v>31.4724</v>
       </c>
       <c r="L5" t="n">
-        <v>14.5604</v>
+        <v>4.2325</v>
       </c>
       <c r="M5" t="n">
-        <v>-35.0774</v>
+        <v>-23.7401</v>
       </c>
       <c r="N5" t="n">
-        <v>-18.3927</v>
+        <v>-12.9007</v>
       </c>
       <c r="O5" t="n">
-        <v>-16.6845</v>
+        <v>-10.8395</v>
       </c>
       <c r="P5" t="n">
-        <v>-8.5373</v>
+        <v>-20.7613</v>
       </c>
       <c r="Q5" t="n">
-        <v>-67.32939999999999</v>
+        <v>-55.8812</v>
       </c>
       <c r="R5" t="n">
-        <v>58.7918</v>
+        <v>35.12</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3996</v>
+        <v>11.2615</v>
       </c>
       <c r="T5" t="n">
-        <v>4.8431</v>
+        <v>6.645</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.4436</v>
+        <v>4.6165</v>
       </c>
       <c r="V5" t="n">
-        <v>26.6107</v>
+        <v>9.7628</v>
       </c>
       <c r="W5" t="n">
-        <v>46.9668</v>
+        <v>22.8624</v>
       </c>
       <c r="X5" t="n">
-        <v>-20.356</v>
+        <v>-13.0997</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. PEÑA LOPEZ</t>
+          <t>I. REBERGEN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>2.229099999999999</v>
+        <v>8.424800000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>6.7338</v>
+        <v>4.445499999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.5045</v>
+        <v>3.979599999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.307899999999999</v>
+        <v>9.726100000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.8532</v>
+        <v>9.1523</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4546999999999999</v>
+        <v>0.5735999999999998</v>
       </c>
       <c r="J6" t="n">
-        <v>14.5451</v>
+        <v>22.9145</v>
       </c>
       <c r="K6" t="n">
-        <v>9.4376</v>
+        <v>15.6331</v>
       </c>
       <c r="L6" t="n">
-        <v>5.1071</v>
+        <v>7.281200000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-18.8526</v>
+        <v>-13.1882</v>
       </c>
       <c r="N6" t="n">
-        <v>-13.291</v>
+        <v>-6.4809</v>
       </c>
       <c r="O6" t="n">
-        <v>-5.561500000000001</v>
+        <v>-6.7073</v>
       </c>
       <c r="P6" t="n">
-        <v>11.0599</v>
+        <v>-8.9253</v>
       </c>
       <c r="Q6" t="n">
-        <v>-21.3437</v>
+        <v>-42.2993</v>
       </c>
       <c r="R6" t="n">
-        <v>32.4035</v>
+        <v>33.3736</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0396</v>
+        <v>-3.6326</v>
       </c>
       <c r="T6" t="n">
-        <v>4.358099999999999</v>
+        <v>-1.8191</v>
       </c>
       <c r="U6" t="n">
-        <v>-5.3974</v>
+        <v>-1.8136</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.4832</v>
+        <v>11.2571</v>
       </c>
       <c r="W6" t="n">
-        <v>9.1746</v>
+        <v>25.6491</v>
       </c>
       <c r="X6" t="n">
-        <v>-12.6578</v>
+        <v>-14.3922</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. PINTOR HENNINGSEN</t>
+          <t>O. PEÑA LOPEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.1249</v>
+        <v>2.5426</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6971</v>
+        <v>3.493600000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4278</v>
+        <v>-0.9510999999999998</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.0702</v>
+        <v>-4.307899999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4212</v>
+        <v>-3.8532</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.649</v>
+        <v>-0.4546999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1942</v>
+        <v>14.5451</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2348</v>
+        <v>9.4376</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0406</v>
+        <v>5.1071</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.8759</v>
+        <v>-18.8526</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1864</v>
+        <v>-13.291</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6896</v>
+        <v>-5.561500000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1941</v>
+        <v>11.0599</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9702</v>
+        <v>-21.3437</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7761</v>
+        <v>32.4035</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8607</v>
+        <v>-0.7262</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5327</v>
+        <v>1.1178</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3279</v>
+        <v>-1.8441</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-3.4832</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>9.1746</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-12.6578</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. REBERGEN</t>
+          <t>B. PINTOR HENNINGSEN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.2853</v>
+        <v>-2.9069</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.0681</v>
+        <v>-1.6971</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2172000000000002</v>
+        <v>-1.2098</v>
       </c>
       <c r="G8" t="n">
-        <v>9.726100000000001</v>
+        <v>-2.0702</v>
       </c>
       <c r="H8" t="n">
-        <v>9.1523</v>
+        <v>-1.4212</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5735999999999998</v>
+        <v>-0.649</v>
       </c>
       <c r="J8" t="n">
-        <v>22.9145</v>
+        <v>-0.1942</v>
       </c>
       <c r="K8" t="n">
-        <v>15.6331</v>
+        <v>-0.2348</v>
       </c>
       <c r="L8" t="n">
-        <v>7.281200000000001</v>
+        <v>0.0406</v>
       </c>
       <c r="M8" t="n">
-        <v>-13.1882</v>
+        <v>-1.8759</v>
       </c>
       <c r="N8" t="n">
-        <v>-6.4809</v>
+        <v>-1.1864</v>
       </c>
       <c r="O8" t="n">
-        <v>-6.7073</v>
+        <v>-0.6896</v>
       </c>
       <c r="P8" t="n">
-        <v>-8.9253</v>
+        <v>-0.1941</v>
       </c>
       <c r="Q8" t="n">
-        <v>-42.2993</v>
+        <v>-0.9702</v>
       </c>
       <c r="R8" t="n">
-        <v>33.3736</v>
+        <v>0.7761</v>
       </c>
       <c r="S8" t="n">
-        <v>-16.3423</v>
+        <v>-0.6426999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-10.3326</v>
+        <v>-0.5327</v>
       </c>
       <c r="U8" t="n">
-        <v>-6.0101</v>
+        <v>-0.1099</v>
       </c>
       <c r="V8" t="n">
-        <v>11.2571</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>25.6491</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-14.3922</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>-7.297899999999999</v>
+        <v>-4.0421</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.238</v>
+        <v>-4.012300000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0597</v>
+        <v>-0.02940000000000031</v>
       </c>
       <c r="G9" t="n">
         <v>-3.076499999999999</v>
@@ -1156,13 +1156,13 @@
         <v>11.8359</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.7334</v>
+        <v>1.5226</v>
       </c>
       <c r="T9" t="n">
-        <v>-3.0698</v>
+        <v>-0.8440000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>1.3366</v>
+        <v>2.3668</v>
       </c>
       <c r="V9" t="n">
         <v>-5.204400000000001</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. GARCÍA PEREZ</t>
+          <t>J. RIES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>-19.1588</v>
+        <v>-17.7974</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7664</v>
+        <v>-13.2851</v>
       </c>
       <c r="F10" t="n">
-        <v>-16.3927</v>
+        <v>-4.512700000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.921</v>
+        <v>-17.2955</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.4963</v>
+        <v>-5.278700000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.4246</v>
+        <v>-12.017</v>
       </c>
       <c r="J10" t="n">
-        <v>4.6602</v>
+        <v>1.6965</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9908</v>
+        <v>6.2162</v>
       </c>
       <c r="L10" t="n">
-        <v>1.6696</v>
+        <v>-4.519800000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-10.5811</v>
+        <v>-18.9918</v>
       </c>
       <c r="N10" t="n">
-        <v>-5.4871</v>
+        <v>-11.4949</v>
       </c>
       <c r="O10" t="n">
-        <v>-5.0942</v>
+        <v>-7.4971</v>
       </c>
       <c r="P10" t="n">
-        <v>2.5224</v>
+        <v>8.1495</v>
       </c>
       <c r="Q10" t="n">
-        <v>-8.1495</v>
+        <v>-20.9558</v>
       </c>
       <c r="R10" t="n">
-        <v>10.6717</v>
+        <v>29.105</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5547</v>
+        <v>-5.7241</v>
       </c>
       <c r="T10" t="n">
-        <v>1.478</v>
+        <v>-2.7318</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9232</v>
+        <v>-2.9927</v>
       </c>
       <c r="V10" t="n">
-        <v>-16.3148</v>
+        <v>-2.9268</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.7551999999999999</v>
+        <v>8.706</v>
       </c>
       <c r="X10" t="n">
-        <v>-15.5595</v>
+        <v>-11.6328</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. RODRÍGUEZ RIVEROL</t>
+          <t>D. OJEDA DAVILA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D11" t="n">
-        <v>-22.5715</v>
+        <v>-18.1755</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.6046</v>
+        <v>-13.2641</v>
       </c>
       <c r="F11" t="n">
-        <v>-13.9671</v>
+        <v>-4.9113</v>
       </c>
       <c r="G11" t="n">
-        <v>-14.1919</v>
+        <v>-24.1729</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.8186</v>
+        <v>-4.6798</v>
       </c>
       <c r="I11" t="n">
-        <v>-11.3733</v>
+        <v>-19.4933</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9313999999999997</v>
+        <v>-5.1185</v>
       </c>
       <c r="K11" t="n">
-        <v>5.458</v>
+        <v>5.4706</v>
       </c>
       <c r="L11" t="n">
-        <v>-4.5267</v>
+        <v>-10.5892</v>
       </c>
       <c r="M11" t="n">
-        <v>-15.1229</v>
+        <v>-19.0544</v>
       </c>
       <c r="N11" t="n">
-        <v>-8.2766</v>
+        <v>-10.1499</v>
       </c>
       <c r="O11" t="n">
-        <v>-6.846</v>
+        <v>-8.903600000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>6.4031</v>
+        <v>8.925699999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>-9.701699999999999</v>
+        <v>-12.6121</v>
       </c>
       <c r="R11" t="n">
-        <v>16.1048</v>
+        <v>21.5376</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.7422</v>
+        <v>0.7280999999999997</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.7503</v>
+        <v>-0.9453999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.9919</v>
+        <v>1.6738</v>
       </c>
       <c r="V11" t="n">
-        <v>-10.0409</v>
+        <v>-3.6567</v>
       </c>
       <c r="W11" t="n">
-        <v>2.9164</v>
+        <v>5.412</v>
       </c>
       <c r="X11" t="n">
-        <v>-12.9571</v>
+        <v>-9.0686</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. OJEDA DAVILA</t>
+          <t>E. GARCÍA PEREZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D12" t="n">
-        <v>-25.4054</v>
+        <v>-19.8512</v>
       </c>
       <c r="E12" t="n">
-        <v>-18.6931</v>
+        <v>-3.9467</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.7121</v>
+        <v>-15.9045</v>
       </c>
       <c r="G12" t="n">
-        <v>-24.1729</v>
+        <v>-5.921</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.6798</v>
+        <v>-2.4963</v>
       </c>
       <c r="I12" t="n">
-        <v>-19.4933</v>
+        <v>-3.4246</v>
       </c>
       <c r="J12" t="n">
-        <v>-5.1185</v>
+        <v>4.6602</v>
       </c>
       <c r="K12" t="n">
-        <v>5.4706</v>
+        <v>2.9908</v>
       </c>
       <c r="L12" t="n">
-        <v>-10.5892</v>
+        <v>1.6696</v>
       </c>
       <c r="M12" t="n">
-        <v>-19.0544</v>
+        <v>-10.5811</v>
       </c>
       <c r="N12" t="n">
-        <v>-10.1499</v>
+        <v>-5.4871</v>
       </c>
       <c r="O12" t="n">
-        <v>-8.903600000000001</v>
+        <v>-5.0942</v>
       </c>
       <c r="P12" t="n">
-        <v>8.925699999999999</v>
+        <v>2.5224</v>
       </c>
       <c r="Q12" t="n">
-        <v>-12.6121</v>
+        <v>-8.1495</v>
       </c>
       <c r="R12" t="n">
-        <v>21.5376</v>
+        <v>10.6717</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.501300000000001</v>
+        <v>-0.1376</v>
       </c>
       <c r="T12" t="n">
-        <v>-6.3744</v>
+        <v>0.2976999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1270999999999999</v>
+        <v>-0.4357</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.6567</v>
+        <v>-16.3148</v>
       </c>
       <c r="W12" t="n">
-        <v>5.412</v>
+        <v>-0.7551999999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-9.0686</v>
+        <v>-15.5595</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. RIES</t>
+          <t>M. RODRÍGUEZ RIVEROL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D13" t="n">
-        <v>-27.4794</v>
+        <v>-20.6441</v>
       </c>
       <c r="E13" t="n">
-        <v>-19.4565</v>
+        <v>-7.761799999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.022300000000001</v>
+        <v>-12.8824</v>
       </c>
       <c r="G13" t="n">
-        <v>-17.2955</v>
+        <v>-14.1919</v>
       </c>
       <c r="H13" t="n">
-        <v>-5.278700000000001</v>
+        <v>-2.8186</v>
       </c>
       <c r="I13" t="n">
-        <v>-12.017</v>
+        <v>-11.3733</v>
       </c>
       <c r="J13" t="n">
-        <v>1.6965</v>
+        <v>0.9313999999999997</v>
       </c>
       <c r="K13" t="n">
-        <v>6.2162</v>
+        <v>5.458</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.519800000000001</v>
+        <v>-4.5267</v>
       </c>
       <c r="M13" t="n">
-        <v>-18.9918</v>
+        <v>-15.1229</v>
       </c>
       <c r="N13" t="n">
-        <v>-11.4949</v>
+        <v>-8.2766</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.4971</v>
+        <v>-6.846</v>
       </c>
       <c r="P13" t="n">
-        <v>8.1495</v>
+        <v>6.4031</v>
       </c>
       <c r="Q13" t="n">
-        <v>-20.9558</v>
+        <v>-9.701699999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>29.105</v>
+        <v>16.1048</v>
       </c>
       <c r="S13" t="n">
-        <v>-15.4062</v>
+        <v>-2.8146</v>
       </c>
       <c r="T13" t="n">
-        <v>-8.903600000000001</v>
+        <v>-1.9074</v>
       </c>
       <c r="U13" t="n">
-        <v>-6.5028</v>
+        <v>-0.9073000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.9268</v>
+        <v>-10.0409</v>
       </c>
       <c r="W13" t="n">
-        <v>8.706</v>
+        <v>2.9164</v>
       </c>
       <c r="X13" t="n">
-        <v>-11.6328</v>
+        <v>-12.9571</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>-30.2818</v>
+        <v>-40.5575</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.7517</v>
+        <v>-19.4761</v>
       </c>
       <c r="F14" t="n">
-        <v>-19.5302</v>
+        <v>-21.0818</v>
       </c>
       <c r="G14" t="n">
         <v>-20.4197</v>
@@ -1546,13 +1546,13 @@
         <v>29.8812</v>
       </c>
       <c r="S14" t="n">
-        <v>11.7731</v>
+        <v>1.4966</v>
       </c>
       <c r="T14" t="n">
-        <v>9.9398</v>
+        <v>1.215</v>
       </c>
       <c r="U14" t="n">
-        <v>1.833</v>
+        <v>0.2813999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-27.0678</v>
@@ -1579,25 +1579,25 @@
         <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>42.61850000000002</v>
+        <v>61.79559999999998</v>
       </c>
       <c r="E15" t="n">
-        <v>97.12740000000002</v>
+        <v>104.2925</v>
       </c>
       <c r="F15" t="n">
-        <v>-54.5082</v>
+        <v>-42.49630000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>-7.383200000000006</v>
+        <v>-7.383199999999999</v>
       </c>
       <c r="H15" t="n">
         <v>-11.8888</v>
       </c>
       <c r="I15" t="n">
-        <v>4.504799999999996</v>
+        <v>4.504799999999989</v>
       </c>
       <c r="J15" t="n">
-        <v>252.9775999999999</v>
+        <v>252.9776</v>
       </c>
       <c r="K15" t="n">
         <v>139.3525</v>
@@ -1624,16 +1624,16 @@
         <v>393.8863</v>
       </c>
       <c r="S15" t="n">
-        <v>-17.1544</v>
+        <v>2.0224</v>
       </c>
       <c r="T15" t="n">
-        <v>-6.562400000000002</v>
+        <v>0.6028000000000002</v>
       </c>
       <c r="U15" t="n">
-        <v>-10.5923</v>
+        <v>1.418999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>43.87310000000001</v>
+        <v>43.87309999999999</v>
       </c>
       <c r="W15" t="n">
         <v>221.3153</v>
